--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Framework_coverage.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Framework_coverage.xlsx
@@ -33,7 +33,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-08-16 17:58 UTC</t>
+    <t>2026-08-17 15:43 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
